--- a/wwwroot/119/BoxBreakingReport.xlsx
+++ b/wwwroot/119/BoxBreakingReport.xlsx
@@ -14,6 +14,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
+    <t>SerialNo</t>
+  </si>
+  <si>
     <t>CatchNo</t>
   </si>
   <si>
@@ -65,10 +68,7 @@
     <t>BoxNo</t>
   </si>
   <si>
-    <t>OmrSerial</t>
-  </si>
-  <si>
-    <t>InnerBundlingSerial</t>
+    <t>Beejak</t>
   </si>
   <si>
     <t>BED103</t>
@@ -92,19 +92,19 @@
     <t>2001</t>
   </si>
   <si>
+    <t>BED104</t>
+  </si>
+  <si>
+    <t>02-11-2026</t>
+  </si>
+  <si>
+    <t>20 to 28</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>BED104</t>
-  </si>
-  <si>
-    <t>02-11-2026</t>
-  </si>
-  <si>
-    <t>20 to 28</t>
-  </si>
-  <si>
-    <t>2002</t>
   </si>
   <si>
     <t>KP/II/1003/25</t>
@@ -1441,8 +1441,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -1467,8 +1472,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1479,90 +1485,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="B1:T292"/>
+  <dimension ref="A1:S292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="16.057085037231445" customWidth="1"/>
-    <col min="3" max="3" width="12.736950874328613" customWidth="1"/>
-    <col min="4" max="4" width="11.54150390625" customWidth="1"/>
+    <col min="3" max="3" width="12.745315551757812" customWidth="1"/>
+    <col min="4" max="4" width="11.811811447143555" customWidth="1"/>
     <col min="5" max="5" width="22.885726928710938" customWidth="1"/>
     <col min="6" max="6" width="13.382554054260254" customWidth="1"/>
-    <col min="7" max="7" width="9.146153450012207" customWidth="1"/>
-    <col min="8" max="8" width="11.75413990020752" customWidth="1"/>
-    <col min="9" max="9" width="10.625441551208496" customWidth="1"/>
+    <col min="7" max="7" width="9.218536376953125" customWidth="1"/>
+    <col min="8" max="8" width="11.907477378845215" customWidth="1"/>
+    <col min="9" max="9" width="10.976926803588867" customWidth="1"/>
     <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="11" max="11" width="10.764904975891113" customWidth="1"/>
-    <col min="12" max="12" width="9.573080062866211" customWidth="1"/>
+    <col min="11" max="11" width="11.134539604187012" customWidth="1"/>
+    <col min="12" max="12" width="9.52771282196045" customWidth="1"/>
     <col min="13" max="13" width="9.140625" customWidth="1"/>
     <col min="14" max="14" width="9.140625" customWidth="1"/>
     <col min="15" max="15" width="9.432053565979004" customWidth="1"/>
     <col min="16" max="16" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="11.96428394317627" customWidth="1"/>
+    <col min="17" max="17" width="11.965397834777832" customWidth="1"/>
     <col min="18" max="18" width="9.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.050959587097168" customWidth="1"/>
-    <col min="20" max="20" width="19.786996841430664" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="0" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
       <c r="B2" s="0" t="s">
         <v>19</v>
       </c>
@@ -1615,15 +1624,15 @@
         <v>25</v>
       </c>
       <c r="S2" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T2" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>20</v>
@@ -1635,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="0">
         <v>720</v>
@@ -1662,7 +1671,7 @@
         <v>28</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3" s="0">
         <v>4</v>
@@ -1671,16 +1680,16 @@
         <v>2880</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
       <c r="B4" s="0" t="s">
         <v>31</v>
       </c>
@@ -1733,13 +1742,13 @@
         <v>33</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
       <c r="B5" s="0" t="s">
         <v>34</v>
       </c>
@@ -1753,7 +1762,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="0">
         <v>30</v>
@@ -1792,13 +1801,13 @@
         <v>35</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T5" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
+      <c r="A6" s="0">
+        <v>5</v>
+      </c>
       <c r="B6" s="0" t="s">
         <v>36</v>
       </c>
@@ -1851,13 +1860,13 @@
         <v>38</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T6" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" s="0">
+        <v>6</v>
+      </c>
       <c r="B7" s="0" t="s">
         <v>39</v>
       </c>
@@ -1871,7 +1880,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="0">
         <v>190</v>
@@ -1910,13 +1919,13 @@
         <v>40</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="0">
+        <v>7</v>
+      </c>
       <c r="B8" s="0" t="s">
         <v>41</v>
       </c>
@@ -1969,13 +1978,13 @@
         <v>43</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T8" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="0">
+        <v>8</v>
+      </c>
       <c r="B9" s="0" t="s">
         <v>44</v>
       </c>
@@ -1989,7 +1998,7 @@
         <v>21</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="0">
         <v>180</v>
@@ -2028,13 +2037,13 @@
         <v>45</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T9" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="0">
+        <v>9</v>
+      </c>
       <c r="B10" s="0" t="s">
         <v>46</v>
       </c>
@@ -2087,13 +2096,13 @@
         <v>48</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T10" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" s="0">
+        <v>10</v>
+      </c>
       <c r="B11" s="0" t="s">
         <v>49</v>
       </c>
@@ -2107,7 +2116,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="0">
         <v>130</v>
@@ -2146,13 +2155,13 @@
         <v>50</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T11" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
+      <c r="A12" s="0">
+        <v>11</v>
+      </c>
       <c r="B12" s="0" t="s">
         <v>51</v>
       </c>
@@ -2205,13 +2214,13 @@
         <v>53</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="0">
+        <v>12</v>
+      </c>
       <c r="B13" s="0" t="s">
         <v>54</v>
       </c>
@@ -2225,7 +2234,7 @@
         <v>21</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="0">
         <v>20</v>
@@ -2264,13 +2273,13 @@
         <v>55</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T13" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="0">
+        <v>13</v>
+      </c>
       <c r="B14" s="0" t="s">
         <v>56</v>
       </c>
@@ -2323,13 +2332,13 @@
         <v>58</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T14" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="0">
+        <v>14</v>
+      </c>
       <c r="B15" s="0" t="s">
         <v>59</v>
       </c>
@@ -2343,7 +2352,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15" s="0">
         <v>140</v>
@@ -2382,13 +2391,13 @@
         <v>60</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="0">
+        <v>15</v>
+      </c>
       <c r="B16" s="0" t="s">
         <v>61</v>
       </c>
@@ -2441,13 +2450,13 @@
         <v>63</v>
       </c>
       <c r="S16" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" s="0">
+        <v>16</v>
+      </c>
       <c r="B17" s="0" t="s">
         <v>64</v>
       </c>
@@ -2461,7 +2470,7 @@
         <v>21</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="0">
         <v>10</v>
@@ -2500,13 +2509,13 @@
         <v>65</v>
       </c>
       <c r="S17" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
+      <c r="A18" s="0">
+        <v>17</v>
+      </c>
       <c r="B18" s="0" t="s">
         <v>66</v>
       </c>
@@ -2559,13 +2568,13 @@
         <v>68</v>
       </c>
       <c r="S18" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T18" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" s="0">
+        <v>18</v>
+      </c>
       <c r="B19" s="0" t="s">
         <v>69</v>
       </c>
@@ -2579,7 +2588,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="0">
         <v>120</v>
@@ -2618,13 +2627,13 @@
         <v>70</v>
       </c>
       <c r="S19" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T19" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" s="0">
+        <v>19</v>
+      </c>
       <c r="B20" s="0" t="s">
         <v>71</v>
       </c>
@@ -2677,13 +2686,13 @@
         <v>73</v>
       </c>
       <c r="S20" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T20" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
+      <c r="A21" s="0">
+        <v>20</v>
+      </c>
       <c r="B21" s="0" t="s">
         <v>74</v>
       </c>
@@ -2697,7 +2706,7 @@
         <v>21</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="0">
         <v>30</v>
@@ -2736,13 +2745,13 @@
         <v>75</v>
       </c>
       <c r="S21" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T21" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
+      <c r="A22" s="0">
+        <v>21</v>
+      </c>
       <c r="B22" s="0" t="s">
         <v>76</v>
       </c>
@@ -2795,13 +2804,13 @@
         <v>78</v>
       </c>
       <c r="S22" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T22" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" s="0">
+        <v>22</v>
+      </c>
       <c r="B23" s="0" t="s">
         <v>79</v>
       </c>
@@ -2815,7 +2824,7 @@
         <v>77</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" s="0">
         <v>30</v>
@@ -2854,13 +2863,13 @@
         <v>80</v>
       </c>
       <c r="S23" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T23" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" s="0">
+        <v>23</v>
+      </c>
       <c r="B24" s="0" t="s">
         <v>81</v>
       </c>
@@ -2913,13 +2922,13 @@
         <v>83</v>
       </c>
       <c r="S24" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T24" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
+      <c r="A25" s="0">
+        <v>24</v>
+      </c>
       <c r="B25" s="0" t="s">
         <v>84</v>
       </c>
@@ -2933,7 +2942,7 @@
         <v>77</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="0">
         <v>150</v>
@@ -2972,13 +2981,13 @@
         <v>85</v>
       </c>
       <c r="S25" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
+      <c r="A26" s="0">
+        <v>25</v>
+      </c>
       <c r="B26" s="0" t="s">
         <v>86</v>
       </c>
@@ -3031,13 +3040,13 @@
         <v>88</v>
       </c>
       <c r="S26" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
         <v>26</v>
       </c>
-      <c r="T26" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
       <c r="B27" s="0" t="s">
         <v>89</v>
       </c>
@@ -3051,7 +3060,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="0">
         <v>120</v>
@@ -3090,13 +3099,13 @@
         <v>91</v>
       </c>
       <c r="S27" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T27" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
+      <c r="A28" s="0">
+        <v>27</v>
+      </c>
       <c r="B28" s="0" t="s">
         <v>92</v>
       </c>
@@ -3149,13 +3158,13 @@
         <v>94</v>
       </c>
       <c r="S28" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T28" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" s="0">
+        <v>28</v>
+      </c>
       <c r="B29" s="0" t="s">
         <v>95</v>
       </c>
@@ -3208,13 +3217,13 @@
         <v>96</v>
       </c>
       <c r="S29" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T29" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
+      <c r="A30" s="0">
+        <v>29</v>
+      </c>
       <c r="B30" s="0" t="s">
         <v>19</v>
       </c>
@@ -3267,15 +3276,15 @@
         <v>99</v>
       </c>
       <c r="S30" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T30" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>97</v>
@@ -3287,7 +3296,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" s="0">
         <v>280</v>
@@ -3326,13 +3335,13 @@
         <v>101</v>
       </c>
       <c r="S31" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T31" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
+      <c r="A32" s="0">
+        <v>31</v>
+      </c>
       <c r="B32" s="0" t="s">
         <v>102</v>
       </c>
@@ -3385,13 +3394,13 @@
         <v>104</v>
       </c>
       <c r="S32" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T32" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" s="0">
+        <v>32</v>
+      </c>
       <c r="B33" s="0" t="s">
         <v>105</v>
       </c>
@@ -3405,7 +3414,7 @@
         <v>77</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" s="0">
         <v>70</v>
@@ -3444,13 +3453,13 @@
         <v>106</v>
       </c>
       <c r="S33" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T33" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" s="0">
+        <v>33</v>
+      </c>
       <c r="B34" s="0" t="s">
         <v>107</v>
       </c>
@@ -3503,13 +3512,13 @@
         <v>108</v>
       </c>
       <c r="S34" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T34" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
+      <c r="A35" s="0">
+        <v>34</v>
+      </c>
       <c r="B35" s="0" t="s">
         <v>109</v>
       </c>
@@ -3562,13 +3571,13 @@
         <v>111</v>
       </c>
       <c r="S35" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T35" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
+      <c r="A36" s="0">
+        <v>35</v>
+      </c>
       <c r="B36" s="0" t="s">
         <v>112</v>
       </c>
@@ -3621,13 +3630,13 @@
         <v>114</v>
       </c>
       <c r="S36" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T36" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
+      <c r="A37" s="0">
+        <v>36</v>
+      </c>
       <c r="B37" s="0" t="s">
         <v>31</v>
       </c>
@@ -3680,13 +3689,13 @@
         <v>117</v>
       </c>
       <c r="S37" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T37" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
+      <c r="A38" s="0">
+        <v>37</v>
+      </c>
       <c r="B38" s="0" t="s">
         <v>34</v>
       </c>
@@ -3700,7 +3709,7 @@
         <v>21</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38" s="0">
         <v>10</v>
@@ -3739,13 +3748,13 @@
         <v>118</v>
       </c>
       <c r="S38" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T38" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
+      <c r="A39" s="0">
+        <v>38</v>
+      </c>
       <c r="B39" s="0" t="s">
         <v>36</v>
       </c>
@@ -3798,13 +3807,13 @@
         <v>120</v>
       </c>
       <c r="S39" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T39" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
+      <c r="A40" s="0">
+        <v>39</v>
+      </c>
       <c r="B40" s="0" t="s">
         <v>39</v>
       </c>
@@ -3818,7 +3827,7 @@
         <v>21</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40" s="0">
         <v>30</v>
@@ -3857,13 +3866,13 @@
         <v>121</v>
       </c>
       <c r="S40" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T40" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
+      <c r="A41" s="0">
+        <v>40</v>
+      </c>
       <c r="B41" s="0" t="s">
         <v>41</v>
       </c>
@@ -3916,13 +3925,13 @@
         <v>123</v>
       </c>
       <c r="S41" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T41" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
+      <c r="A42" s="0">
+        <v>41</v>
+      </c>
       <c r="B42" s="0" t="s">
         <v>44</v>
       </c>
@@ -3936,7 +3945,7 @@
         <v>21</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G42" s="0">
         <v>90</v>
@@ -3975,13 +3984,13 @@
         <v>124</v>
       </c>
       <c r="S42" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T42" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
+      <c r="A43" s="0">
+        <v>42</v>
+      </c>
       <c r="B43" s="0" t="s">
         <v>46</v>
       </c>
@@ -4034,13 +4043,13 @@
         <v>125</v>
       </c>
       <c r="S43" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T43" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
+      <c r="A44" s="0">
+        <v>43</v>
+      </c>
       <c r="B44" s="0" t="s">
         <v>49</v>
       </c>
@@ -4054,7 +4063,7 @@
         <v>21</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G44" s="0">
         <v>70</v>
@@ -4093,13 +4102,13 @@
         <v>126</v>
       </c>
       <c r="S44" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T44" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
+      <c r="A45" s="0">
+        <v>44</v>
+      </c>
       <c r="B45" s="0" t="s">
         <v>56</v>
       </c>
@@ -4152,13 +4161,13 @@
         <v>128</v>
       </c>
       <c r="S45" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T45" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
+      <c r="A46" s="0">
+        <v>45</v>
+      </c>
       <c r="B46" s="0" t="s">
         <v>59</v>
       </c>
@@ -4172,7 +4181,7 @@
         <v>21</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G46" s="0">
         <v>60</v>
@@ -4211,13 +4220,13 @@
         <v>129</v>
       </c>
       <c r="S46" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T46" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
+      <c r="A47" s="0">
+        <v>46</v>
+      </c>
       <c r="B47" s="0" t="s">
         <v>66</v>
       </c>
@@ -4270,13 +4279,13 @@
         <v>131</v>
       </c>
       <c r="S47" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T47" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
+      <c r="A48" s="0">
+        <v>47</v>
+      </c>
       <c r="B48" s="0" t="s">
         <v>69</v>
       </c>
@@ -4290,7 +4299,7 @@
         <v>21</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48" s="0">
         <v>20</v>
@@ -4329,13 +4338,13 @@
         <v>132</v>
       </c>
       <c r="S48" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T48" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
+      <c r="A49" s="0">
+        <v>48</v>
+      </c>
       <c r="B49" s="0" t="s">
         <v>71</v>
       </c>
@@ -4388,13 +4397,13 @@
         <v>134</v>
       </c>
       <c r="S49" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T49" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
+      <c r="A50" s="0">
+        <v>49</v>
+      </c>
       <c r="B50" s="0" t="s">
         <v>74</v>
       </c>
@@ -4408,7 +4417,7 @@
         <v>21</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50" s="0">
         <v>10</v>
@@ -4447,13 +4456,13 @@
         <v>135</v>
       </c>
       <c r="S50" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T50" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
+      <c r="A51" s="0">
+        <v>50</v>
+      </c>
       <c r="B51" s="0" t="s">
         <v>76</v>
       </c>
@@ -4506,13 +4515,13 @@
         <v>137</v>
       </c>
       <c r="S51" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T51" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
+      <c r="A52" s="0">
+        <v>51</v>
+      </c>
       <c r="B52" s="0" t="s">
         <v>79</v>
       </c>
@@ -4526,7 +4535,7 @@
         <v>77</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G52" s="0">
         <v>20</v>
@@ -4565,13 +4574,13 @@
         <v>138</v>
       </c>
       <c r="S52" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T52" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
+      <c r="A53" s="0">
+        <v>52</v>
+      </c>
       <c r="B53" s="0" t="s">
         <v>81</v>
       </c>
@@ -4624,13 +4633,13 @@
         <v>140</v>
       </c>
       <c r="S53" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T53" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
+      <c r="A54" s="0">
+        <v>53</v>
+      </c>
       <c r="B54" s="0" t="s">
         <v>84</v>
       </c>
@@ -4644,7 +4653,7 @@
         <v>77</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G54" s="0">
         <v>10</v>
@@ -4683,13 +4692,13 @@
         <v>141</v>
       </c>
       <c r="S54" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T54" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
+      <c r="A55" s="0">
+        <v>54</v>
+      </c>
       <c r="B55" s="0" t="s">
         <v>41</v>
       </c>
@@ -4742,13 +4751,13 @@
         <v>144</v>
       </c>
       <c r="S55" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T55" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
+      <c r="A56" s="0">
+        <v>55</v>
+      </c>
       <c r="B56" s="0" t="s">
         <v>44</v>
       </c>
@@ -4762,7 +4771,7 @@
         <v>21</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G56" s="0">
         <v>10</v>
@@ -4801,13 +4810,13 @@
         <v>145</v>
       </c>
       <c r="S56" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T56" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
+      <c r="A57" s="0">
+        <v>56</v>
+      </c>
       <c r="B57" s="0" t="s">
         <v>56</v>
       </c>
@@ -4860,13 +4869,13 @@
         <v>147</v>
       </c>
       <c r="S57" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T57" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
+      <c r="A58" s="0">
+        <v>57</v>
+      </c>
       <c r="B58" s="0" t="s">
         <v>59</v>
       </c>
@@ -4880,7 +4889,7 @@
         <v>21</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G58" s="0">
         <v>10</v>
@@ -4919,13 +4928,13 @@
         <v>148</v>
       </c>
       <c r="S58" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T58" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
+      <c r="A59" s="0">
+        <v>58</v>
+      </c>
       <c r="B59" s="0" t="s">
         <v>66</v>
       </c>
@@ -4978,13 +4987,13 @@
         <v>150</v>
       </c>
       <c r="S59" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T59" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
+      <c r="A60" s="0">
+        <v>59</v>
+      </c>
       <c r="B60" s="0" t="s">
         <v>69</v>
       </c>
@@ -4998,7 +5007,7 @@
         <v>21</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G60" s="0">
         <v>10</v>
@@ -5037,13 +5046,13 @@
         <v>151</v>
       </c>
       <c r="S60" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T60" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
+      <c r="A61" s="0">
+        <v>60</v>
+      </c>
       <c r="B61" s="0" t="s">
         <v>41</v>
       </c>
@@ -5096,13 +5105,13 @@
         <v>154</v>
       </c>
       <c r="S61" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T61" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
+      <c r="A62" s="0">
+        <v>61</v>
+      </c>
       <c r="B62" s="0" t="s">
         <v>44</v>
       </c>
@@ -5116,7 +5125,7 @@
         <v>21</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62" s="0">
         <v>40</v>
@@ -5155,13 +5164,13 @@
         <v>155</v>
       </c>
       <c r="S62" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T62" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
+      <c r="A63" s="0">
+        <v>62</v>
+      </c>
       <c r="B63" s="0" t="s">
         <v>56</v>
       </c>
@@ -5214,13 +5223,13 @@
         <v>157</v>
       </c>
       <c r="S63" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T63" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
+      <c r="A64" s="0">
+        <v>63</v>
+      </c>
       <c r="B64" s="0" t="s">
         <v>59</v>
       </c>
@@ -5234,7 +5243,7 @@
         <v>21</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G64" s="0">
         <v>20</v>
@@ -5273,13 +5282,13 @@
         <v>158</v>
       </c>
       <c r="S64" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T64" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
+      <c r="A65" s="0">
+        <v>64</v>
+      </c>
       <c r="B65" s="0" t="s">
         <v>66</v>
       </c>
@@ -5332,13 +5341,13 @@
         <v>159</v>
       </c>
       <c r="S65" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T65" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
+      <c r="A66" s="0">
+        <v>65</v>
+      </c>
       <c r="B66" s="0" t="s">
         <v>69</v>
       </c>
@@ -5352,7 +5361,7 @@
         <v>21</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66" s="0">
         <v>20</v>
@@ -5391,13 +5400,13 @@
         <v>160</v>
       </c>
       <c r="S66" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T66" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
+      <c r="A67" s="0">
+        <v>66</v>
+      </c>
       <c r="B67" s="0" t="s">
         <v>161</v>
       </c>
@@ -5450,13 +5459,13 @@
         <v>163</v>
       </c>
       <c r="S67" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T67" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68">
+      <c r="A68" s="0">
+        <v>67</v>
+      </c>
       <c r="B68" s="0" t="s">
         <v>19</v>
       </c>
@@ -5509,15 +5518,15 @@
         <v>166</v>
       </c>
       <c r="S68" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>68</v>
+      </c>
+      <c r="B69" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T68" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C69" s="0" t="s">
         <v>164</v>
@@ -5529,7 +5538,7 @@
         <v>21</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G69" s="0">
         <v>400</v>
@@ -5568,13 +5577,13 @@
         <v>167</v>
       </c>
       <c r="S69" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T69" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
+      <c r="A70" s="0">
+        <v>69</v>
+      </c>
       <c r="B70" s="0" t="s">
         <v>31</v>
       </c>
@@ -5627,13 +5636,13 @@
         <v>169</v>
       </c>
       <c r="S70" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T70" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
+      <c r="A71" s="0">
+        <v>70</v>
+      </c>
       <c r="B71" s="0" t="s">
         <v>34</v>
       </c>
@@ -5647,7 +5656,7 @@
         <v>21</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G71" s="0">
         <v>90</v>
@@ -5686,13 +5695,13 @@
         <v>170</v>
       </c>
       <c r="S71" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T71" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
+      <c r="A72" s="0">
+        <v>71</v>
+      </c>
       <c r="B72" s="0" t="s">
         <v>36</v>
       </c>
@@ -5745,13 +5754,13 @@
         <v>172</v>
       </c>
       <c r="S72" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T72" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73">
+      <c r="A73" s="0">
+        <v>72</v>
+      </c>
       <c r="B73" s="0" t="s">
         <v>39</v>
       </c>
@@ -5765,7 +5774,7 @@
         <v>21</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G73" s="0">
         <v>340</v>
@@ -5804,13 +5813,13 @@
         <v>173</v>
       </c>
       <c r="S73" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T73" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
+      <c r="A74" s="0">
+        <v>73</v>
+      </c>
       <c r="B74" s="0" t="s">
         <v>41</v>
       </c>
@@ -5863,13 +5872,13 @@
         <v>174</v>
       </c>
       <c r="S74" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T74" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75">
+      <c r="A75" s="0">
+        <v>74</v>
+      </c>
       <c r="B75" s="0" t="s">
         <v>44</v>
       </c>
@@ -5883,7 +5892,7 @@
         <v>21</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G75" s="0">
         <v>390</v>
@@ -5922,13 +5931,13 @@
         <v>175</v>
       </c>
       <c r="S75" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T75" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
+      <c r="A76" s="0">
+        <v>75</v>
+      </c>
       <c r="B76" s="0" t="s">
         <v>46</v>
       </c>
@@ -5981,13 +5990,13 @@
         <v>176</v>
       </c>
       <c r="S76" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T76" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77">
+      <c r="A77" s="0">
+        <v>76</v>
+      </c>
       <c r="B77" s="0" t="s">
         <v>49</v>
       </c>
@@ -6001,7 +6010,7 @@
         <v>21</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G77" s="0">
         <v>380</v>
@@ -6040,13 +6049,13 @@
         <v>177</v>
       </c>
       <c r="S77" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T77" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78">
+      <c r="A78" s="0">
+        <v>77</v>
+      </c>
       <c r="B78" s="0" t="s">
         <v>56</v>
       </c>
@@ -6099,13 +6108,13 @@
         <v>179</v>
       </c>
       <c r="S78" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T78" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79">
+      <c r="A79" s="0">
+        <v>78</v>
+      </c>
       <c r="B79" s="0" t="s">
         <v>59</v>
       </c>
@@ -6119,7 +6128,7 @@
         <v>21</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G79" s="0">
         <v>330</v>
@@ -6158,13 +6167,13 @@
         <v>180</v>
       </c>
       <c r="S79" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T79" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80">
+      <c r="A80" s="0">
+        <v>79</v>
+      </c>
       <c r="B80" s="0" t="s">
         <v>66</v>
       </c>
@@ -6217,13 +6226,13 @@
         <v>181</v>
       </c>
       <c r="S80" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T80" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81">
+      <c r="A81" s="0">
+        <v>80</v>
+      </c>
       <c r="B81" s="0" t="s">
         <v>69</v>
       </c>
@@ -6237,7 +6246,7 @@
         <v>21</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G81" s="0">
         <v>50</v>
@@ -6276,13 +6285,13 @@
         <v>182</v>
       </c>
       <c r="S81" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T81" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
+      <c r="A82" s="0">
+        <v>81</v>
+      </c>
       <c r="B82" s="0" t="s">
         <v>71</v>
       </c>
@@ -6335,13 +6344,13 @@
         <v>183</v>
       </c>
       <c r="S82" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T82" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
+      <c r="A83" s="0">
+        <v>82</v>
+      </c>
       <c r="B83" s="0" t="s">
         <v>74</v>
       </c>
@@ -6355,7 +6364,7 @@
         <v>21</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G83" s="0">
         <v>70</v>
@@ -6394,13 +6403,13 @@
         <v>184</v>
       </c>
       <c r="S83" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T83" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84">
+      <c r="A84" s="0">
+        <v>83</v>
+      </c>
       <c r="B84" s="0" t="s">
         <v>76</v>
       </c>
@@ -6453,13 +6462,13 @@
         <v>185</v>
       </c>
       <c r="S84" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T84" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
+      <c r="A85" s="0">
+        <v>84</v>
+      </c>
       <c r="B85" s="0" t="s">
         <v>79</v>
       </c>
@@ -6473,7 +6482,7 @@
         <v>77</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G85" s="0">
         <v>80</v>
@@ -6512,13 +6521,13 @@
         <v>186</v>
       </c>
       <c r="S85" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T85" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
+      <c r="A86" s="0">
+        <v>85</v>
+      </c>
       <c r="B86" s="0" t="s">
         <v>81</v>
       </c>
@@ -6571,13 +6580,13 @@
         <v>187</v>
       </c>
       <c r="S86" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T86" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
+      <c r="A87" s="0">
+        <v>86</v>
+      </c>
       <c r="B87" s="0" t="s">
         <v>84</v>
       </c>
@@ -6591,7 +6600,7 @@
         <v>77</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G87" s="0">
         <v>230</v>
@@ -6630,13 +6639,13 @@
         <v>188</v>
       </c>
       <c r="S87" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T87" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
+      <c r="A88" s="0">
+        <v>87</v>
+      </c>
       <c r="B88" s="0" t="s">
         <v>86</v>
       </c>
@@ -6689,13 +6698,13 @@
         <v>189</v>
       </c>
       <c r="S88" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T88" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89">
+      <c r="A89" s="0">
+        <v>88</v>
+      </c>
       <c r="B89" s="0" t="s">
         <v>89</v>
       </c>
@@ -6709,7 +6718,7 @@
         <v>21</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G89" s="0">
         <v>70</v>
@@ -6748,13 +6757,13 @@
         <v>190</v>
       </c>
       <c r="S89" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T89" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90">
+      <c r="A90" s="0">
+        <v>89</v>
+      </c>
       <c r="B90" s="0" t="s">
         <v>92</v>
       </c>
@@ -6807,13 +6816,13 @@
         <v>191</v>
       </c>
       <c r="S90" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T90" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91">
+      <c r="A91" s="0">
+        <v>90</v>
+      </c>
       <c r="B91" s="0" t="s">
         <v>192</v>
       </c>
@@ -6866,13 +6875,13 @@
         <v>193</v>
       </c>
       <c r="S91" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T91" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92">
+      <c r="A92" s="0">
+        <v>91</v>
+      </c>
       <c r="B92" s="0" t="s">
         <v>194</v>
       </c>
@@ -6886,7 +6895,7 @@
         <v>21</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G92" s="0">
         <v>70</v>
@@ -6925,13 +6934,13 @@
         <v>195</v>
       </c>
       <c r="S92" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T92" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93">
+      <c r="A93" s="0">
+        <v>92</v>
+      </c>
       <c r="B93" s="0" t="s">
         <v>196</v>
       </c>
@@ -6984,13 +6993,13 @@
         <v>197</v>
       </c>
       <c r="S93" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T93" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
+      <c r="A94" s="0">
+        <v>93</v>
+      </c>
       <c r="B94" s="0" t="s">
         <v>19</v>
       </c>
@@ -7043,15 +7052,15 @@
         <v>200</v>
       </c>
       <c r="S94" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0">
+        <v>94</v>
+      </c>
+      <c r="B95" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T94" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C95" s="0" t="s">
         <v>198</v>
@@ -7063,7 +7072,7 @@
         <v>21</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G95" s="0">
         <v>470</v>
@@ -7102,13 +7111,13 @@
         <v>202</v>
       </c>
       <c r="S95" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T95" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96">
+      <c r="A96" s="0">
+        <v>95</v>
+      </c>
       <c r="B96" s="0" t="s">
         <v>31</v>
       </c>
@@ -7161,13 +7170,13 @@
         <v>203</v>
       </c>
       <c r="S96" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T96" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97">
+      <c r="A97" s="0">
+        <v>96</v>
+      </c>
       <c r="B97" s="0" t="s">
         <v>34</v>
       </c>
@@ -7181,7 +7190,7 @@
         <v>21</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G97" s="0">
         <v>60</v>
@@ -7220,13 +7229,13 @@
         <v>204</v>
       </c>
       <c r="S97" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T97" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
+      <c r="A98" s="0">
+        <v>97</v>
+      </c>
       <c r="B98" s="0" t="s">
         <v>36</v>
       </c>
@@ -7279,13 +7288,13 @@
         <v>206</v>
       </c>
       <c r="S98" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T98" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99">
+      <c r="A99" s="0">
+        <v>98</v>
+      </c>
       <c r="B99" s="0" t="s">
         <v>39</v>
       </c>
@@ -7299,7 +7308,7 @@
         <v>21</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G99" s="0">
         <v>170</v>
@@ -7338,13 +7347,13 @@
         <v>207</v>
       </c>
       <c r="S99" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T99" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100">
+      <c r="A100" s="0">
+        <v>99</v>
+      </c>
       <c r="B100" s="0" t="s">
         <v>41</v>
       </c>
@@ -7397,13 +7406,13 @@
         <v>209</v>
       </c>
       <c r="S100" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T100" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101">
+      <c r="A101" s="0">
+        <v>100</v>
+      </c>
       <c r="B101" s="0" t="s">
         <v>44</v>
       </c>
@@ -7417,7 +7426,7 @@
         <v>21</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G101" s="0">
         <v>230</v>
@@ -7456,13 +7465,13 @@
         <v>210</v>
       </c>
       <c r="S101" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T101" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
+      <c r="A102" s="0">
+        <v>101</v>
+      </c>
       <c r="B102" s="0" t="s">
         <v>46</v>
       </c>
@@ -7515,13 +7524,13 @@
         <v>212</v>
       </c>
       <c r="S102" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T102" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
+      <c r="A103" s="0">
+        <v>102</v>
+      </c>
       <c r="B103" s="0" t="s">
         <v>49</v>
       </c>
@@ -7535,7 +7544,7 @@
         <v>21</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G103" s="0">
         <v>220</v>
@@ -7574,13 +7583,13 @@
         <v>213</v>
       </c>
       <c r="S103" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T103" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104">
+      <c r="A104" s="0">
+        <v>103</v>
+      </c>
       <c r="B104" s="0" t="s">
         <v>56</v>
       </c>
@@ -7633,13 +7642,13 @@
         <v>215</v>
       </c>
       <c r="S104" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T104" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105">
+      <c r="A105" s="0">
+        <v>104</v>
+      </c>
       <c r="B105" s="0" t="s">
         <v>59</v>
       </c>
@@ -7653,7 +7662,7 @@
         <v>21</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G105" s="0">
         <v>200</v>
@@ -7692,13 +7701,13 @@
         <v>216</v>
       </c>
       <c r="S105" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T105" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
+      <c r="A106" s="0">
+        <v>105</v>
+      </c>
       <c r="B106" s="0" t="s">
         <v>66</v>
       </c>
@@ -7751,13 +7760,13 @@
         <v>218</v>
       </c>
       <c r="S106" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T106" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107">
+      <c r="A107" s="0">
+        <v>106</v>
+      </c>
       <c r="B107" s="0" t="s">
         <v>69</v>
       </c>
@@ -7771,7 +7780,7 @@
         <v>21</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G107" s="0">
         <v>50</v>
@@ -7810,13 +7819,13 @@
         <v>219</v>
       </c>
       <c r="S107" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T107" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
+      <c r="A108" s="0">
+        <v>107</v>
+      </c>
       <c r="B108" s="0" t="s">
         <v>76</v>
       </c>
@@ -7869,13 +7878,13 @@
         <v>221</v>
       </c>
       <c r="S108" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T108" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109">
+      <c r="A109" s="0">
+        <v>108</v>
+      </c>
       <c r="B109" s="0" t="s">
         <v>79</v>
       </c>
@@ -7889,7 +7898,7 @@
         <v>77</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G109" s="0">
         <v>80</v>
@@ -7928,13 +7937,13 @@
         <v>222</v>
       </c>
       <c r="S109" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T109" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110">
+      <c r="A110" s="0">
+        <v>109</v>
+      </c>
       <c r="B110" s="0" t="s">
         <v>81</v>
       </c>
@@ -7987,13 +7996,13 @@
         <v>224</v>
       </c>
       <c r="S110" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T110" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111">
+      <c r="A111" s="0">
+        <v>110</v>
+      </c>
       <c r="B111" s="0" t="s">
         <v>84</v>
       </c>
@@ -8007,7 +8016,7 @@
         <v>77</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G111" s="0">
         <v>140</v>
@@ -8046,13 +8055,13 @@
         <v>225</v>
       </c>
       <c r="S111" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T111" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112">
+      <c r="A112" s="0">
+        <v>111</v>
+      </c>
       <c r="B112" s="0" t="s">
         <v>86</v>
       </c>
@@ -8105,13 +8114,13 @@
         <v>226</v>
       </c>
       <c r="S112" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T112" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113">
+      <c r="A113" s="0">
+        <v>112</v>
+      </c>
       <c r="B113" s="0" t="s">
         <v>89</v>
       </c>
@@ -8125,7 +8134,7 @@
         <v>21</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G113" s="0">
         <v>130</v>
@@ -8164,13 +8173,13 @@
         <v>227</v>
       </c>
       <c r="S113" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T113" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
+      <c r="A114" s="0">
+        <v>113</v>
+      </c>
       <c r="B114" s="0" t="s">
         <v>92</v>
       </c>
@@ -8223,13 +8232,13 @@
         <v>228</v>
       </c>
       <c r="S114" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T114" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115">
+      <c r="A115" s="0">
+        <v>114</v>
+      </c>
       <c r="B115" s="0" t="s">
         <v>192</v>
       </c>
@@ -8282,13 +8291,13 @@
         <v>230</v>
       </c>
       <c r="S115" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T115" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116">
+      <c r="A116" s="0">
+        <v>115</v>
+      </c>
       <c r="B116" s="0" t="s">
         <v>194</v>
       </c>
@@ -8302,7 +8311,7 @@
         <v>21</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G116" s="0">
         <v>70</v>
@@ -8341,13 +8350,13 @@
         <v>231</v>
       </c>
       <c r="S116" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T116" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117">
+      <c r="A117" s="0">
+        <v>116</v>
+      </c>
       <c r="B117" s="0" t="s">
         <v>196</v>
       </c>
@@ -8400,13 +8409,13 @@
         <v>232</v>
       </c>
       <c r="S117" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T117" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118">
+      <c r="A118" s="0">
+        <v>117</v>
+      </c>
       <c r="B118" s="0" t="s">
         <v>41</v>
       </c>
@@ -8459,13 +8468,13 @@
         <v>234</v>
       </c>
       <c r="S118" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T118" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
+      <c r="A119" s="0">
+        <v>118</v>
+      </c>
       <c r="B119" s="0" t="s">
         <v>44</v>
       </c>
@@ -8479,7 +8488,7 @@
         <v>21</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G119" s="0">
         <v>70</v>
@@ -8518,13 +8527,13 @@
         <v>235</v>
       </c>
       <c r="S119" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T119" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120">
+      <c r="A120" s="0">
+        <v>119</v>
+      </c>
       <c r="B120" s="0" t="s">
         <v>56</v>
       </c>
@@ -8577,13 +8586,13 @@
         <v>236</v>
       </c>
       <c r="S120" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T120" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121">
+      <c r="A121" s="0">
+        <v>120</v>
+      </c>
       <c r="B121" s="0" t="s">
         <v>59</v>
       </c>
@@ -8597,7 +8606,7 @@
         <v>21</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G121" s="0">
         <v>100</v>
@@ -8636,13 +8645,13 @@
         <v>237</v>
       </c>
       <c r="S121" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T121" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122">
+      <c r="A122" s="0">
+        <v>121</v>
+      </c>
       <c r="B122" s="0" t="s">
         <v>76</v>
       </c>
@@ -8695,13 +8704,13 @@
         <v>239</v>
       </c>
       <c r="S122" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T122" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123">
+      <c r="A123" s="0">
+        <v>122</v>
+      </c>
       <c r="B123" s="0" t="s">
         <v>79</v>
       </c>
@@ -8715,7 +8724,7 @@
         <v>77</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G123" s="0">
         <v>20</v>
@@ -8754,13 +8763,13 @@
         <v>240</v>
       </c>
       <c r="S123" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T123" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124">
+      <c r="A124" s="0">
+        <v>123</v>
+      </c>
       <c r="B124" s="0" t="s">
         <v>81</v>
       </c>
@@ -8813,13 +8822,13 @@
         <v>241</v>
       </c>
       <c r="S124" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T124" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125">
+      <c r="A125" s="0">
+        <v>124</v>
+      </c>
       <c r="B125" s="0" t="s">
         <v>84</v>
       </c>
@@ -8833,7 +8842,7 @@
         <v>77</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G125" s="0">
         <v>10</v>
@@ -8872,13 +8881,13 @@
         <v>242</v>
       </c>
       <c r="S125" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T125" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126">
+      <c r="A126" s="0">
+        <v>125</v>
+      </c>
       <c r="B126" s="0" t="s">
         <v>31</v>
       </c>
@@ -8931,13 +8940,13 @@
         <v>244</v>
       </c>
       <c r="S126" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T126" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127">
+      <c r="A127" s="0">
+        <v>126</v>
+      </c>
       <c r="B127" s="0" t="s">
         <v>34</v>
       </c>
@@ -8951,7 +8960,7 @@
         <v>21</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G127" s="0">
         <v>10</v>
@@ -8990,13 +8999,13 @@
         <v>245</v>
       </c>
       <c r="S127" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T127" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128">
+      <c r="A128" s="0">
+        <v>127</v>
+      </c>
       <c r="B128" s="0" t="s">
         <v>41</v>
       </c>
@@ -9049,13 +9058,13 @@
         <v>247</v>
       </c>
       <c r="S128" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T128" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129">
+      <c r="A129" s="0">
+        <v>128</v>
+      </c>
       <c r="B129" s="0" t="s">
         <v>44</v>
       </c>
@@ -9069,7 +9078,7 @@
         <v>21</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G129" s="0">
         <v>30</v>
@@ -9108,13 +9117,13 @@
         <v>248</v>
       </c>
       <c r="S129" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T129" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130">
+      <c r="A130" s="0">
+        <v>129</v>
+      </c>
       <c r="B130" s="0" t="s">
         <v>56</v>
       </c>
@@ -9167,13 +9176,13 @@
         <v>250</v>
       </c>
       <c r="S130" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T130" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131">
+      <c r="A131" s="0">
+        <v>130</v>
+      </c>
       <c r="B131" s="0" t="s">
         <v>59</v>
       </c>
@@ -9187,7 +9196,7 @@
         <v>21</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G131" s="0">
         <v>40</v>
@@ -9226,13 +9235,13 @@
         <v>251</v>
       </c>
       <c r="S131" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T131" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132">
+      <c r="A132" s="0">
+        <v>131</v>
+      </c>
       <c r="B132" s="0" t="s">
         <v>31</v>
       </c>
@@ -9285,13 +9294,13 @@
         <v>253</v>
       </c>
       <c r="S132" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T132" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133">
+      <c r="A133" s="0">
+        <v>132</v>
+      </c>
       <c r="B133" s="0" t="s">
         <v>34</v>
       </c>
@@ -9305,7 +9314,7 @@
         <v>21</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G133" s="0">
         <v>30</v>
@@ -9344,13 +9353,13 @@
         <v>254</v>
       </c>
       <c r="S133" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T133" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134">
+      <c r="A134" s="0">
+        <v>133</v>
+      </c>
       <c r="B134" s="0" t="s">
         <v>41</v>
       </c>
@@ -9403,13 +9412,13 @@
         <v>256</v>
       </c>
       <c r="S134" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T134" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135">
+      <c r="A135" s="0">
+        <v>134</v>
+      </c>
       <c r="B135" s="0" t="s">
         <v>44</v>
       </c>
@@ -9423,7 +9432,7 @@
         <v>21</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G135" s="0">
         <v>100</v>
@@ -9462,13 +9471,13 @@
         <v>257</v>
       </c>
       <c r="S135" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T135" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136">
+      <c r="A136" s="0">
+        <v>135</v>
+      </c>
       <c r="B136" s="0" t="s">
         <v>41</v>
       </c>
@@ -9521,13 +9530,13 @@
         <v>260</v>
       </c>
       <c r="S136" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T136" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137">
+      <c r="A137" s="0">
+        <v>136</v>
+      </c>
       <c r="B137" s="0" t="s">
         <v>44</v>
       </c>
@@ -9541,7 +9550,7 @@
         <v>21</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G137" s="0">
         <v>50</v>
@@ -9580,13 +9589,13 @@
         <v>261</v>
       </c>
       <c r="S137" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T137" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138">
+      <c r="A138" s="0">
+        <v>137</v>
+      </c>
       <c r="B138" s="0" t="s">
         <v>56</v>
       </c>
@@ -9639,13 +9648,13 @@
         <v>262</v>
       </c>
       <c r="S138" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T138" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139">
+      <c r="A139" s="0">
+        <v>138</v>
+      </c>
       <c r="B139" s="0" t="s">
         <v>59</v>
       </c>
@@ -9659,7 +9668,7 @@
         <v>21</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G139" s="0">
         <v>70</v>
@@ -9698,13 +9707,13 @@
         <v>263</v>
       </c>
       <c r="S139" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T139" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140">
+      <c r="A140" s="0">
+        <v>139</v>
+      </c>
       <c r="B140" s="0" t="s">
         <v>76</v>
       </c>
@@ -9757,13 +9766,13 @@
         <v>265</v>
       </c>
       <c r="S140" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T140" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141">
+      <c r="A141" s="0">
+        <v>140</v>
+      </c>
       <c r="B141" s="0" t="s">
         <v>79</v>
       </c>
@@ -9777,7 +9786,7 @@
         <v>77</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G141" s="0">
         <v>10</v>
@@ -9816,13 +9825,13 @@
         <v>266</v>
       </c>
       <c r="S141" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T141" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142">
+      <c r="A142" s="0">
+        <v>141</v>
+      </c>
       <c r="B142" s="0" t="s">
         <v>267</v>
       </c>
@@ -9875,13 +9884,13 @@
         <v>270</v>
       </c>
       <c r="S142" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T142" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143">
+      <c r="A143" s="0">
+        <v>142</v>
+      </c>
       <c r="B143" s="0" t="s">
         <v>271</v>
       </c>
@@ -9934,13 +9943,13 @@
         <v>270</v>
       </c>
       <c r="S143" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T143" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144">
+      <c r="A144" s="0">
+        <v>143</v>
+      </c>
       <c r="B144" s="0" t="s">
         <v>272</v>
       </c>
@@ -9993,13 +10002,13 @@
         <v>270</v>
       </c>
       <c r="S144" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T144" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145">
+      <c r="A145" s="0">
+        <v>144</v>
+      </c>
       <c r="B145" s="0" t="s">
         <v>273</v>
       </c>
@@ -10052,13 +10061,13 @@
         <v>274</v>
       </c>
       <c r="S145" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T145" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146">
+      <c r="A146" s="0">
+        <v>145</v>
+      </c>
       <c r="B146" s="0" t="s">
         <v>275</v>
       </c>
@@ -10111,13 +10120,13 @@
         <v>274</v>
       </c>
       <c r="S146" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T146" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147">
+      <c r="A147" s="0">
+        <v>146</v>
+      </c>
       <c r="B147" s="0" t="s">
         <v>276</v>
       </c>
@@ -10170,13 +10179,13 @@
         <v>278</v>
       </c>
       <c r="S147" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T147" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148">
+      <c r="A148" s="0">
+        <v>147</v>
+      </c>
       <c r="B148" s="0" t="s">
         <v>279</v>
       </c>
@@ -10229,13 +10238,13 @@
         <v>281</v>
       </c>
       <c r="S148" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T148" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="149">
+      <c r="A149" s="0">
+        <v>148</v>
+      </c>
       <c r="B149" s="0" t="s">
         <v>282</v>
       </c>
@@ -10288,13 +10297,13 @@
         <v>281</v>
       </c>
       <c r="S149" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T149" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150">
+      <c r="A150" s="0">
+        <v>149</v>
+      </c>
       <c r="B150" s="0" t="s">
         <v>283</v>
       </c>
@@ -10347,13 +10356,13 @@
         <v>284</v>
       </c>
       <c r="S150" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T150" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151">
+      <c r="A151" s="0">
+        <v>150</v>
+      </c>
       <c r="B151" s="0" t="s">
         <v>285</v>
       </c>
@@ -10406,13 +10415,13 @@
         <v>286</v>
       </c>
       <c r="S151" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T151" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152">
+      <c r="A152" s="0">
+        <v>151</v>
+      </c>
       <c r="B152" s="0" t="s">
         <v>287</v>
       </c>
@@ -10426,7 +10435,7 @@
         <v>77</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G152" s="0">
         <v>110</v>
@@ -10465,13 +10474,13 @@
         <v>288</v>
       </c>
       <c r="S152" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T152" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153">
+      <c r="A153" s="0">
+        <v>152</v>
+      </c>
       <c r="B153" s="0" t="s">
         <v>19</v>
       </c>
@@ -10524,15 +10533,15 @@
         <v>290</v>
       </c>
       <c r="S153" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0">
+        <v>153</v>
+      </c>
+      <c r="B154" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T153" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>268</v>
@@ -10544,7 +10553,7 @@
         <v>21</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G154" s="0">
         <v>110</v>
@@ -10583,13 +10592,13 @@
         <v>292</v>
       </c>
       <c r="S154" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T154" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155">
+      <c r="A155" s="0">
+        <v>154</v>
+      </c>
       <c r="B155" s="0" t="s">
         <v>293</v>
       </c>
@@ -10642,13 +10651,13 @@
         <v>296</v>
       </c>
       <c r="S155" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T155" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156">
+      <c r="A156" s="0">
+        <v>155</v>
+      </c>
       <c r="B156" s="0" t="s">
         <v>297</v>
       </c>
@@ -10662,7 +10671,7 @@
         <v>21</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G156" s="0">
         <v>10</v>
@@ -10701,13 +10710,13 @@
         <v>299</v>
       </c>
       <c r="S156" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T156" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157">
+      <c r="A157" s="0">
+        <v>156</v>
+      </c>
       <c r="B157" s="0" t="s">
         <v>300</v>
       </c>
@@ -10760,13 +10769,13 @@
         <v>301</v>
       </c>
       <c r="S157" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T157" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158">
+      <c r="A158" s="0">
+        <v>157</v>
+      </c>
       <c r="B158" s="0" t="s">
         <v>302</v>
       </c>
@@ -10819,13 +10828,13 @@
         <v>303</v>
       </c>
       <c r="S158" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T158" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159">
+      <c r="A159" s="0">
+        <v>158</v>
+      </c>
       <c r="B159" s="0" t="s">
         <v>304</v>
       </c>
@@ -10878,13 +10887,13 @@
         <v>305</v>
       </c>
       <c r="S159" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T159" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160">
+      <c r="A160" s="0">
+        <v>159</v>
+      </c>
       <c r="B160" s="0" t="s">
         <v>306</v>
       </c>
@@ -10937,13 +10946,13 @@
         <v>308</v>
       </c>
       <c r="S160" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T160" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161">
+      <c r="A161" s="0">
+        <v>160</v>
+      </c>
       <c r="B161" s="0" t="s">
         <v>267</v>
       </c>
@@ -10996,13 +11005,13 @@
         <v>309</v>
       </c>
       <c r="S161" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T161" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162">
+      <c r="A162" s="0">
+        <v>161</v>
+      </c>
       <c r="B162" s="0" t="s">
         <v>271</v>
       </c>
@@ -11055,13 +11064,13 @@
         <v>309</v>
       </c>
       <c r="S162" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T162" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163">
+      <c r="A163" s="0">
+        <v>162</v>
+      </c>
       <c r="B163" s="0" t="s">
         <v>272</v>
       </c>
@@ -11114,13 +11123,13 @@
         <v>309</v>
       </c>
       <c r="S163" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T163" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164">
+      <c r="A164" s="0">
+        <v>163</v>
+      </c>
       <c r="B164" s="0" t="s">
         <v>273</v>
       </c>
@@ -11173,13 +11182,13 @@
         <v>311</v>
       </c>
       <c r="S164" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T164" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165">
+      <c r="A165" s="0">
+        <v>164</v>
+      </c>
       <c r="B165" s="0" t="s">
         <v>275</v>
       </c>
@@ -11232,13 +11241,13 @@
         <v>311</v>
       </c>
       <c r="S165" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T165" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166">
+      <c r="A166" s="0">
+        <v>165</v>
+      </c>
       <c r="B166" s="0" t="s">
         <v>276</v>
       </c>
@@ -11291,13 +11300,13 @@
         <v>312</v>
       </c>
       <c r="S166" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T166" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167">
+      <c r="A167" s="0">
+        <v>166</v>
+      </c>
       <c r="B167" s="0" t="s">
         <v>279</v>
       </c>
@@ -11350,13 +11359,13 @@
         <v>313</v>
       </c>
       <c r="S167" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T167" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="168">
+      <c r="A168" s="0">
+        <v>167</v>
+      </c>
       <c r="B168" s="0" t="s">
         <v>282</v>
       </c>
@@ -11409,13 +11418,13 @@
         <v>313</v>
       </c>
       <c r="S168" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T168" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169">
+      <c r="A169" s="0">
+        <v>168</v>
+      </c>
       <c r="B169" s="0" t="s">
         <v>283</v>
       </c>
@@ -11468,13 +11477,13 @@
         <v>314</v>
       </c>
       <c r="S169" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T169" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170">
+      <c r="A170" s="0">
+        <v>169</v>
+      </c>
       <c r="B170" s="0" t="s">
         <v>285</v>
       </c>
@@ -11527,13 +11536,13 @@
         <v>315</v>
       </c>
       <c r="S170" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T170" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171">
+      <c r="A171" s="0">
+        <v>170</v>
+      </c>
       <c r="B171" s="0" t="s">
         <v>287</v>
       </c>
@@ -11547,7 +11556,7 @@
         <v>77</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G171" s="0">
         <v>10</v>
@@ -11586,13 +11595,13 @@
         <v>316</v>
       </c>
       <c r="S171" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T171" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172">
+      <c r="A172" s="0">
+        <v>171</v>
+      </c>
       <c r="B172" s="0" t="s">
         <v>317</v>
       </c>
@@ -11645,13 +11654,13 @@
         <v>318</v>
       </c>
       <c r="S172" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T172" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="173">
+      <c r="A173" s="0">
+        <v>172</v>
+      </c>
       <c r="B173" s="0" t="s">
         <v>319</v>
       </c>
@@ -11665,7 +11674,7 @@
         <v>77</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G173" s="0">
         <v>10</v>
@@ -11704,13 +11713,13 @@
         <v>320</v>
       </c>
       <c r="S173" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T173" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174">
+      <c r="A174" s="0">
+        <v>173</v>
+      </c>
       <c r="B174" s="0" t="s">
         <v>321</v>
       </c>
@@ -11763,13 +11772,13 @@
         <v>322</v>
       </c>
       <c r="S174" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T174" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175">
+      <c r="A175" s="0">
+        <v>174</v>
+      </c>
       <c r="B175" s="0" t="s">
         <v>323</v>
       </c>
@@ -11822,13 +11831,13 @@
         <v>324</v>
       </c>
       <c r="S175" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T175" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176">
+      <c r="A176" s="0">
+        <v>175</v>
+      </c>
       <c r="B176" s="0" t="s">
         <v>19</v>
       </c>
@@ -11881,15 +11890,15 @@
         <v>326</v>
       </c>
       <c r="S176" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0">
+        <v>176</v>
+      </c>
+      <c r="B177" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T176" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C177" s="0" t="s">
         <v>294</v>
@@ -11901,7 +11910,7 @@
         <v>21</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G177" s="0">
         <v>120</v>
@@ -11940,13 +11949,13 @@
         <v>328</v>
       </c>
       <c r="S177" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T177" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178">
+      <c r="A178" s="0">
+        <v>177</v>
+      </c>
       <c r="B178" s="0" t="s">
         <v>329</v>
       </c>
@@ -11999,13 +12008,13 @@
         <v>330</v>
       </c>
       <c r="S178" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T178" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179">
+      <c r="A179" s="0">
+        <v>178</v>
+      </c>
       <c r="B179" s="0" t="s">
         <v>331</v>
       </c>
@@ -12019,7 +12028,7 @@
         <v>77</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G179" s="0">
         <v>10</v>
@@ -12058,13 +12067,13 @@
         <v>332</v>
       </c>
       <c r="S179" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T179" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180">
+      <c r="A180" s="0">
+        <v>179</v>
+      </c>
       <c r="B180" s="0" t="s">
         <v>333</v>
       </c>
@@ -12117,13 +12126,13 @@
         <v>334</v>
       </c>
       <c r="S180" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T180" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="181">
+      <c r="A181" s="0">
+        <v>180</v>
+      </c>
       <c r="B181" s="0" t="s">
         <v>335</v>
       </c>
@@ -12176,13 +12185,13 @@
         <v>336</v>
       </c>
       <c r="S181" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T181" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="182">
+      <c r="A182" s="0">
+        <v>181</v>
+      </c>
       <c r="B182" s="0" t="s">
         <v>337</v>
       </c>
@@ -12235,13 +12244,13 @@
         <v>339</v>
       </c>
       <c r="S182" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T182" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183">
+      <c r="A183" s="0">
+        <v>182</v>
+      </c>
       <c r="B183" s="0" t="s">
         <v>340</v>
       </c>
@@ -12255,7 +12264,7 @@
         <v>77</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G183" s="0">
         <v>10</v>
@@ -12294,13 +12303,13 @@
         <v>341</v>
       </c>
       <c r="S183" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T183" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184">
+      <c r="A184" s="0">
+        <v>183</v>
+      </c>
       <c r="B184" s="0" t="s">
         <v>31</v>
       </c>
@@ -12353,13 +12362,13 @@
         <v>343</v>
       </c>
       <c r="S184" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T184" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="185">
+      <c r="A185" s="0">
+        <v>184</v>
+      </c>
       <c r="B185" s="0" t="s">
         <v>34</v>
       </c>
@@ -12373,7 +12382,7 @@
         <v>21</v>
       </c>
       <c r="F185" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G185" s="0">
         <v>20</v>
@@ -12412,13 +12421,13 @@
         <v>344</v>
       </c>
       <c r="S185" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T185" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186">
+      <c r="A186" s="0">
+        <v>185</v>
+      </c>
       <c r="B186" s="0" t="s">
         <v>36</v>
       </c>
@@ -12471,13 +12480,13 @@
         <v>346</v>
       </c>
       <c r="S186" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T186" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="187">
+      <c r="A187" s="0">
+        <v>186</v>
+      </c>
       <c r="B187" s="0" t="s">
         <v>39</v>
       </c>
@@ -12491,7 +12500,7 @@
         <v>21</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G187" s="0">
         <v>40</v>
@@ -12530,13 +12539,13 @@
         <v>347</v>
       </c>
       <c r="S187" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T187" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="188">
+      <c r="A188" s="0">
+        <v>187</v>
+      </c>
       <c r="B188" s="0" t="s">
         <v>41</v>
       </c>
@@ -12589,13 +12598,13 @@
         <v>349</v>
       </c>
       <c r="S188" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T188" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="189">
+      <c r="A189" s="0">
+        <v>188</v>
+      </c>
       <c r="B189" s="0" t="s">
         <v>44</v>
       </c>
@@ -12609,7 +12618,7 @@
         <v>21</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G189" s="0">
         <v>70</v>
@@ -12648,13 +12657,13 @@
         <v>350</v>
       </c>
       <c r="S189" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T189" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190">
+      <c r="A190" s="0">
+        <v>189</v>
+      </c>
       <c r="B190" s="0" t="s">
         <v>46</v>
       </c>
@@ -12707,13 +12716,13 @@
         <v>352</v>
       </c>
       <c r="S190" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T190" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191">
+      <c r="A191" s="0">
+        <v>190</v>
+      </c>
       <c r="B191" s="0" t="s">
         <v>49</v>
       </c>
@@ -12727,7 +12736,7 @@
         <v>21</v>
       </c>
       <c r="F191" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G191" s="0">
         <v>50</v>
@@ -12766,13 +12775,13 @@
         <v>353</v>
       </c>
       <c r="S191" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T191" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="192">
+      <c r="A192" s="0">
+        <v>191</v>
+      </c>
       <c r="B192" s="0" t="s">
         <v>51</v>
       </c>
@@ -12825,13 +12834,13 @@
         <v>354</v>
       </c>
       <c r="S192" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T192" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="193">
+      <c r="A193" s="0">
+        <v>192</v>
+      </c>
       <c r="B193" s="0" t="s">
         <v>54</v>
       </c>
@@ -12845,7 +12854,7 @@
         <v>21</v>
       </c>
       <c r="F193" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G193" s="0">
         <v>10</v>
@@ -12884,13 +12893,13 @@
         <v>355</v>
       </c>
       <c r="S193" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T193" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="194">
+      <c r="A194" s="0">
+        <v>193</v>
+      </c>
       <c r="B194" s="0" t="s">
         <v>56</v>
       </c>
@@ -12943,13 +12952,13 @@
         <v>357</v>
       </c>
       <c r="S194" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T194" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="195">
+      <c r="A195" s="0">
+        <v>194</v>
+      </c>
       <c r="B195" s="0" t="s">
         <v>59</v>
       </c>
@@ -12963,7 +12972,7 @@
         <v>21</v>
       </c>
       <c r="F195" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G195" s="0">
         <v>60</v>
@@ -13002,13 +13011,13 @@
         <v>358</v>
       </c>
       <c r="S195" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T195" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="196">
+      <c r="A196" s="0">
+        <v>195</v>
+      </c>
       <c r="B196" s="0" t="s">
         <v>61</v>
       </c>
@@ -13061,13 +13070,13 @@
         <v>359</v>
       </c>
       <c r="S196" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T196" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197">
+      <c r="A197" s="0">
+        <v>196</v>
+      </c>
       <c r="B197" s="0" t="s">
         <v>64</v>
       </c>
@@ -13081,7 +13090,7 @@
         <v>21</v>
       </c>
       <c r="F197" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G197" s="0">
         <v>10</v>
@@ -13120,13 +13129,13 @@
         <v>360</v>
       </c>
       <c r="S197" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T197" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="198">
+      <c r="A198" s="0">
+        <v>197</v>
+      </c>
       <c r="B198" s="0" t="s">
         <v>66</v>
       </c>
@@ -13179,13 +13188,13 @@
         <v>362</v>
       </c>
       <c r="S198" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T198" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199">
+      <c r="A199" s="0">
+        <v>198</v>
+      </c>
       <c r="B199" s="0" t="s">
         <v>69</v>
       </c>
@@ -13199,7 +13208,7 @@
         <v>21</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G199" s="0">
         <v>20</v>
@@ -13238,13 +13247,13 @@
         <v>363</v>
       </c>
       <c r="S199" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T199" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="200">
+      <c r="A200" s="0">
+        <v>199</v>
+      </c>
       <c r="B200" s="0" t="s">
         <v>71</v>
       </c>
@@ -13297,13 +13306,13 @@
         <v>364</v>
       </c>
       <c r="S200" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T200" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="201">
+      <c r="A201" s="0">
+        <v>200</v>
+      </c>
       <c r="B201" s="0" t="s">
         <v>74</v>
       </c>
@@ -13317,7 +13326,7 @@
         <v>21</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G201" s="0">
         <v>10</v>
@@ -13356,13 +13365,13 @@
         <v>365</v>
       </c>
       <c r="S201" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T201" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="202">
+      <c r="A202" s="0">
+        <v>201</v>
+      </c>
       <c r="B202" s="0" t="s">
         <v>76</v>
       </c>
@@ -13415,13 +13424,13 @@
         <v>367</v>
       </c>
       <c r="S202" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T202" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="203">
+      <c r="A203" s="0">
+        <v>202</v>
+      </c>
       <c r="B203" s="0" t="s">
         <v>79</v>
       </c>
@@ -13435,7 +13444,7 @@
         <v>77</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G203" s="0">
         <v>20</v>
@@ -13474,13 +13483,13 @@
         <v>368</v>
       </c>
       <c r="S203" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T203" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="204">
+      <c r="A204" s="0">
+        <v>203</v>
+      </c>
       <c r="B204" s="0" t="s">
         <v>81</v>
       </c>
@@ -13533,13 +13542,13 @@
         <v>370</v>
       </c>
       <c r="S204" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T204" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="205">
+      <c r="A205" s="0">
+        <v>204</v>
+      </c>
       <c r="B205" s="0" t="s">
         <v>84</v>
       </c>
@@ -13553,7 +13562,7 @@
         <v>77</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G205" s="0">
         <v>30</v>
@@ -13592,13 +13601,13 @@
         <v>371</v>
       </c>
       <c r="S205" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T205" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="206">
+      <c r="A206" s="0">
+        <v>205</v>
+      </c>
       <c r="B206" s="0" t="s">
         <v>161</v>
       </c>
@@ -13651,13 +13660,13 @@
         <v>372</v>
       </c>
       <c r="S206" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T206" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="207">
+      <c r="A207" s="0">
+        <v>206</v>
+      </c>
       <c r="B207" s="0" t="s">
         <v>373</v>
       </c>
@@ -13710,13 +13719,13 @@
         <v>372</v>
       </c>
       <c r="S207" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T207" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="208">
+      <c r="A208" s="0">
+        <v>207</v>
+      </c>
       <c r="B208" s="0" t="s">
         <v>374</v>
       </c>
@@ -13730,7 +13739,7 @@
         <v>77</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G208" s="0">
         <v>10</v>
@@ -13769,13 +13778,13 @@
         <v>375</v>
       </c>
       <c r="S208" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T208" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="209">
+      <c r="A209" s="0">
+        <v>208</v>
+      </c>
       <c r="B209" s="0" t="s">
         <v>86</v>
       </c>
@@ -13828,13 +13837,13 @@
         <v>376</v>
       </c>
       <c r="S209" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T209" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="210">
+      <c r="A210" s="0">
+        <v>209</v>
+      </c>
       <c r="B210" s="0" t="s">
         <v>89</v>
       </c>
@@ -13848,7 +13857,7 @@
         <v>21</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G210" s="0">
         <v>20</v>
@@ -13887,13 +13896,13 @@
         <v>377</v>
       </c>
       <c r="S210" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T210" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="211">
+      <c r="A211" s="0">
+        <v>210</v>
+      </c>
       <c r="B211" s="0" t="s">
         <v>92</v>
       </c>
@@ -13946,13 +13955,13 @@
         <v>378</v>
       </c>
       <c r="S211" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T211" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="212">
+      <c r="A212" s="0">
+        <v>211</v>
+      </c>
       <c r="B212" s="0" t="s">
         <v>102</v>
       </c>
@@ -14005,13 +14014,13 @@
         <v>379</v>
       </c>
       <c r="S212" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T212" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="213">
+      <c r="A213" s="0">
+        <v>212</v>
+      </c>
       <c r="B213" s="0" t="s">
         <v>105</v>
       </c>
@@ -14025,7 +14034,7 @@
         <v>77</v>
       </c>
       <c r="F213" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G213" s="0">
         <v>10</v>
@@ -14064,13 +14073,13 @@
         <v>380</v>
       </c>
       <c r="S213" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T213" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="214">
+      <c r="A214" s="0">
+        <v>213</v>
+      </c>
       <c r="B214" s="0" t="s">
         <v>107</v>
       </c>
@@ -14123,13 +14132,13 @@
         <v>381</v>
       </c>
       <c r="S214" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T214" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="215">
+      <c r="A215" s="0">
+        <v>214</v>
+      </c>
       <c r="B215" s="0" t="s">
         <v>109</v>
       </c>
@@ -14182,13 +14191,13 @@
         <v>382</v>
       </c>
       <c r="S215" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T215" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="216">
+      <c r="A216" s="0">
+        <v>215</v>
+      </c>
       <c r="B216" s="0" t="s">
         <v>112</v>
       </c>
@@ -14241,13 +14250,13 @@
         <v>383</v>
       </c>
       <c r="S216" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T216" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="217">
+      <c r="A217" s="0">
+        <v>216</v>
+      </c>
       <c r="B217" s="0" t="s">
         <v>95</v>
       </c>
@@ -14300,13 +14309,13 @@
         <v>384</v>
       </c>
       <c r="S217" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T217" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="218">
+      <c r="A218" s="0">
+        <v>217</v>
+      </c>
       <c r="B218" s="0" t="s">
         <v>385</v>
       </c>
@@ -14320,7 +14329,7 @@
         <v>77</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G218" s="0">
         <v>10</v>
@@ -14359,13 +14368,13 @@
         <v>386</v>
       </c>
       <c r="S218" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T218" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="219">
+      <c r="A219" s="0">
+        <v>218</v>
+      </c>
       <c r="B219" s="0" t="s">
         <v>387</v>
       </c>
@@ -14418,13 +14427,13 @@
         <v>388</v>
       </c>
       <c r="S219" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T219" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="220">
+      <c r="A220" s="0">
+        <v>219</v>
+      </c>
       <c r="B220" s="0" t="s">
         <v>389</v>
       </c>
@@ -14477,13 +14486,13 @@
         <v>390</v>
       </c>
       <c r="S220" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T220" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="221">
+      <c r="A221" s="0">
+        <v>220</v>
+      </c>
       <c r="B221" s="0" t="s">
         <v>391</v>
       </c>
@@ -14536,13 +14545,13 @@
         <v>392</v>
       </c>
       <c r="S221" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T221" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="222">
+      <c r="A222" s="0">
+        <v>221</v>
+      </c>
       <c r="B222" s="0" t="s">
         <v>393</v>
       </c>
@@ -14595,13 +14604,13 @@
         <v>394</v>
       </c>
       <c r="S222" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T222" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="223">
+      <c r="A223" s="0">
+        <v>222</v>
+      </c>
       <c r="B223" s="0" t="s">
         <v>395</v>
       </c>
@@ -14615,7 +14624,7 @@
         <v>77</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G223" s="0">
         <v>10</v>
@@ -14654,13 +14663,13 @@
         <v>396</v>
       </c>
       <c r="S223" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T223" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="224">
+      <c r="A224" s="0">
+        <v>223</v>
+      </c>
       <c r="B224" s="0" t="s">
         <v>192</v>
       </c>
@@ -14713,13 +14722,13 @@
         <v>397</v>
       </c>
       <c r="S224" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T224" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
+      <c r="A225" s="0">
+        <v>224</v>
+      </c>
       <c r="B225" s="0" t="s">
         <v>194</v>
       </c>
@@ -14733,7 +14742,7 @@
         <v>21</v>
       </c>
       <c r="F225" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G225" s="0">
         <v>10</v>
@@ -14772,13 +14781,13 @@
         <v>398</v>
       </c>
       <c r="S225" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T225" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226">
+      <c r="A226" s="0">
+        <v>225</v>
+      </c>
       <c r="B226" s="0" t="s">
         <v>196</v>
       </c>
@@ -14831,13 +14840,13 @@
         <v>399</v>
       </c>
       <c r="S226" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T226" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="227">
+      <c r="A227" s="0">
+        <v>226</v>
+      </c>
       <c r="B227" s="0" t="s">
         <v>293</v>
       </c>
@@ -14890,13 +14899,13 @@
         <v>401</v>
       </c>
       <c r="S227" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T227" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="228">
+      <c r="A228" s="0">
+        <v>227</v>
+      </c>
       <c r="B228" s="0" t="s">
         <v>297</v>
       </c>
@@ -14910,7 +14919,7 @@
         <v>21</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G228" s="0">
         <v>60</v>
@@ -14949,13 +14958,13 @@
         <v>402</v>
       </c>
       <c r="S228" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T228" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="229">
+      <c r="A229" s="0">
+        <v>228</v>
+      </c>
       <c r="B229" s="0" t="s">
         <v>300</v>
       </c>
@@ -15008,13 +15017,13 @@
         <v>403</v>
       </c>
       <c r="S229" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T229" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="230">
+      <c r="A230" s="0">
+        <v>229</v>
+      </c>
       <c r="B230" s="0" t="s">
         <v>302</v>
       </c>
@@ -15067,13 +15076,13 @@
         <v>404</v>
       </c>
       <c r="S230" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T230" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="231">
+      <c r="A231" s="0">
+        <v>230</v>
+      </c>
       <c r="B231" s="0" t="s">
         <v>304</v>
       </c>
@@ -15126,13 +15135,13 @@
         <v>405</v>
       </c>
       <c r="S231" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T231" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="232">
+      <c r="A232" s="0">
+        <v>231</v>
+      </c>
       <c r="B232" s="0" t="s">
         <v>306</v>
       </c>
@@ -15185,13 +15194,13 @@
         <v>406</v>
       </c>
       <c r="S232" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T232" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233">
+      <c r="A233" s="0">
+        <v>232</v>
+      </c>
       <c r="B233" s="0" t="s">
         <v>267</v>
       </c>
@@ -15244,13 +15253,13 @@
         <v>408</v>
       </c>
       <c r="S233" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T233" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="234">
+      <c r="A234" s="0">
+        <v>233</v>
+      </c>
       <c r="B234" s="0" t="s">
         <v>271</v>
       </c>
@@ -15303,13 +15312,13 @@
         <v>408</v>
       </c>
       <c r="S234" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T234" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="235">
+      <c r="A235" s="0">
+        <v>234</v>
+      </c>
       <c r="B235" s="0" t="s">
         <v>272</v>
       </c>
@@ -15362,13 +15371,13 @@
         <v>408</v>
       </c>
       <c r="S235" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T235" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="236">
+      <c r="A236" s="0">
+        <v>235</v>
+      </c>
       <c r="B236" s="0" t="s">
         <v>273</v>
       </c>
@@ -15421,13 +15430,13 @@
         <v>410</v>
       </c>
       <c r="S236" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T236" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="237">
+      <c r="A237" s="0">
+        <v>236</v>
+      </c>
       <c r="B237" s="0" t="s">
         <v>275</v>
       </c>
@@ -15480,13 +15489,13 @@
         <v>410</v>
       </c>
       <c r="S237" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T237" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="238">
+      <c r="A238" s="0">
+        <v>237</v>
+      </c>
       <c r="B238" s="0" t="s">
         <v>279</v>
       </c>
@@ -15539,13 +15548,13 @@
         <v>411</v>
       </c>
       <c r="S238" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T238" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="239">
+      <c r="A239" s="0">
+        <v>238</v>
+      </c>
       <c r="B239" s="0" t="s">
         <v>282</v>
       </c>
@@ -15598,13 +15607,13 @@
         <v>411</v>
       </c>
       <c r="S239" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T239" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="240">
+      <c r="A240" s="0">
+        <v>239</v>
+      </c>
       <c r="B240" s="0" t="s">
         <v>283</v>
       </c>
@@ -15657,13 +15666,13 @@
         <v>412</v>
       </c>
       <c r="S240" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T240" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="241">
+      <c r="A241" s="0">
+        <v>240</v>
+      </c>
       <c r="B241" s="0" t="s">
         <v>317</v>
       </c>
@@ -15716,13 +15725,13 @@
         <v>413</v>
       </c>
       <c r="S241" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T241" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="242">
+      <c r="A242" s="0">
+        <v>241</v>
+      </c>
       <c r="B242" s="0" t="s">
         <v>319</v>
       </c>
@@ -15736,7 +15745,7 @@
         <v>77</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G242" s="0">
         <v>70</v>
@@ -15775,13 +15784,13 @@
         <v>414</v>
       </c>
       <c r="S242" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T242" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="243">
+      <c r="A243" s="0">
+        <v>242</v>
+      </c>
       <c r="B243" s="0" t="s">
         <v>321</v>
       </c>
@@ -15834,13 +15843,13 @@
         <v>415</v>
       </c>
       <c r="S243" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T243" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="244">
+      <c r="A244" s="0">
+        <v>243</v>
+      </c>
       <c r="B244" s="0" t="s">
         <v>323</v>
       </c>
@@ -15893,13 +15902,13 @@
         <v>416</v>
       </c>
       <c r="S244" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T244" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="245">
+      <c r="A245" s="0">
+        <v>244</v>
+      </c>
       <c r="B245" s="0" t="s">
         <v>19</v>
       </c>
@@ -15952,15 +15961,15 @@
         <v>418</v>
       </c>
       <c r="S245" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0">
+        <v>245</v>
+      </c>
+      <c r="B246" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="T245" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="B246" s="0" t="s">
-        <v>27</v>
       </c>
       <c r="C246" s="0" t="s">
         <v>400</v>
@@ -15972,7 +15981,7 @@
         <v>21</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G246" s="0">
         <v>330</v>
@@ -16011,13 +16020,13 @@
         <v>420</v>
       </c>
       <c r="S246" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T246" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="247">
+      <c r="A247" s="0">
+        <v>246</v>
+      </c>
       <c r="B247" s="0" t="s">
         <v>329</v>
       </c>
@@ -16070,13 +16079,13 @@
         <v>421</v>
       </c>
       <c r="S247" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T247" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="248">
+      <c r="A248" s="0">
+        <v>247</v>
+      </c>
       <c r="B248" s="0" t="s">
         <v>331</v>
       </c>
@@ -16090,7 +16099,7 @@
         <v>77</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G248" s="0">
         <v>40</v>
@@ -16129,13 +16138,13 @@
         <v>422</v>
       </c>
       <c r="S248" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T248" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="249">
+      <c r="A249" s="0">
+        <v>248</v>
+      </c>
       <c r="B249" s="0" t="s">
         <v>333</v>
       </c>
@@ -16188,13 +16197,13 @@
         <v>423</v>
       </c>
       <c r="S249" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T249" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="250">
+      <c r="A250" s="0">
+        <v>249</v>
+      </c>
       <c r="B250" s="0" t="s">
         <v>335</v>
       </c>
@@ -16247,13 +16256,13 @@
         <v>424</v>
       </c>
       <c r="S250" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T250" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="251">
+      <c r="A251" s="0">
+        <v>250</v>
+      </c>
       <c r="B251" s="0" t="s">
         <v>337</v>
       </c>
@@ -16306,13 +16315,13 @@
         <v>425</v>
       </c>
       <c r="S251" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T251" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="252">
+      <c r="A252" s="0">
+        <v>251</v>
+      </c>
       <c r="B252" s="0" t="s">
         <v>340</v>
       </c>
@@ -16326,7 +16335,7 @@
         <v>77</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G252" s="0">
         <v>50</v>
@@ -16365,13 +16374,13 @@
         <v>426</v>
       </c>
       <c r="S252" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T252" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="253">
+      <c r="A253" s="0">
+        <v>252</v>
+      </c>
       <c r="B253" s="0" t="s">
         <v>31</v>
       </c>
@@ -16424,13 +16433,13 @@
         <v>427</v>
       </c>
       <c r="S253" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T253" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="254">
+      <c r="A254" s="0">
+        <v>253</v>
+      </c>
       <c r="B254" s="0" t="s">
         <v>34</v>
       </c>
@@ -16444,7 +16453,7 @@
         <v>21</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G254" s="0">
         <v>10</v>
@@ -16483,13 +16492,13 @@
         <v>428</v>
       </c>
       <c r="S254" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T254" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="255">
+      <c r="A255" s="0">
+        <v>254</v>
+      </c>
       <c r="B255" s="0" t="s">
         <v>36</v>
       </c>
@@ -16542,13 +16551,13 @@
         <v>430</v>
       </c>
       <c r="S255" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T255" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="256">
+      <c r="A256" s="0">
+        <v>255</v>
+      </c>
       <c r="B256" s="0" t="s">
         <v>39</v>
       </c>
@@ -16562,7 +16571,7 @@
         <v>21</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G256" s="0">
         <v>20</v>
@@ -16601,13 +16610,13 @@
         <v>431</v>
       </c>
       <c r="S256" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T256" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="257">
+      <c r="A257" s="0">
+        <v>256</v>
+      </c>
       <c r="B257" s="0" t="s">
         <v>41</v>
       </c>
@@ -16660,13 +16669,13 @@
         <v>433</v>
       </c>
       <c r="S257" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T257" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="258">
+      <c r="A258" s="0">
+        <v>257</v>
+      </c>
       <c r="B258" s="0" t="s">
         <v>44</v>
       </c>
@@ -16680,7 +16689,7 @@
         <v>21</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G258" s="0">
         <v>40</v>
@@ -16719,13 +16728,13 @@
         <v>434</v>
       </c>
       <c r="S258" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T258" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="259">
+      <c r="A259" s="0">
+        <v>258</v>
+      </c>
       <c r="B259" s="0" t="s">
         <v>46</v>
       </c>
@@ -16778,13 +16787,13 @@
         <v>436</v>
       </c>
       <c r="S259" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T259" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="260">
+      <c r="A260" s="0">
+        <v>259</v>
+      </c>
       <c r="B260" s="0" t="s">
         <v>49</v>
       </c>
@@ -16798,7 +16807,7 @@
         <v>21</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G260" s="0">
         <v>40</v>
@@ -16837,13 +16846,13 @@
         <v>437</v>
       </c>
       <c r="S260" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T260" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="261">
+      <c r="A261" s="0">
+        <v>260</v>
+      </c>
       <c r="B261" s="0" t="s">
         <v>51</v>
       </c>
@@ -16896,13 +16905,13 @@
         <v>438</v>
       </c>
       <c r="S261" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T261" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="262">
+      <c r="A262" s="0">
+        <v>261</v>
+      </c>
       <c r="B262" s="0" t="s">
         <v>54</v>
       </c>
@@ -16916,7 +16925,7 @@
         <v>21</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G262" s="0">
         <v>10</v>
@@ -16955,13 +16964,13 @@
         <v>439</v>
       </c>
       <c r="S262" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T262" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="263">
+      <c r="A263" s="0">
+        <v>262</v>
+      </c>
       <c r="B263" s="0" t="s">
         <v>56</v>
       </c>
@@ -17014,13 +17023,13 @@
         <v>440</v>
       </c>
       <c r="S263" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T263" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="264">
+      <c r="A264" s="0">
+        <v>263</v>
+      </c>
       <c r="B264" s="0" t="s">
         <v>59</v>
       </c>
@@ -17034,7 +17043,7 @@
         <v>21</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G264" s="0">
         <v>40</v>
@@ -17073,13 +17082,13 @@
         <v>441</v>
       </c>
       <c r="S264" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T264" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="265">
+      <c r="A265" s="0">
+        <v>264</v>
+      </c>
       <c r="B265" s="0" t="s">
         <v>66</v>
       </c>
@@ -17132,13 +17141,13 @@
         <v>443</v>
       </c>
       <c r="S265" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T265" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="266">
+      <c r="A266" s="0">
+        <v>265</v>
+      </c>
       <c r="B266" s="0" t="s">
         <v>69</v>
       </c>
@@ -17152,7 +17161,7 @@
         <v>21</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G266" s="0">
         <v>40</v>
@@ -17191,13 +17200,13 @@
         <v>444</v>
       </c>
       <c r="S266" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T266" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="267">
+      <c r="A267" s="0">
+        <v>266</v>
+      </c>
       <c r="B267" s="0" t="s">
         <v>71</v>
       </c>
@@ -17250,13 +17259,13 @@
         <v>445</v>
       </c>
       <c r="S267" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T267" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="268">
+      <c r="A268" s="0">
+        <v>267</v>
+      </c>
       <c r="B268" s="0" t="s">
         <v>74</v>
       </c>
@@ -17270,7 +17279,7 @@
         <v>21</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G268" s="0">
         <v>10</v>
@@ -17309,13 +17318,13 @@
         <v>446</v>
       </c>
       <c r="S268" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T268" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="269">
+      <c r="A269" s="0">
+        <v>268</v>
+      </c>
       <c r="B269" s="0" t="s">
         <v>76</v>
       </c>
@@ -17368,13 +17377,13 @@
         <v>447</v>
       </c>
       <c r="S269" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T269" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="270">
+      <c r="A270" s="0">
+        <v>269</v>
+      </c>
       <c r="B270" s="0" t="s">
         <v>79</v>
       </c>
@@ -17388,7 +17397,7 @@
         <v>77</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G270" s="0">
         <v>10</v>
@@ -17427,13 +17436,13 @@
         <v>448</v>
       </c>
       <c r="S270" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T270" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="271">
+      <c r="A271" s="0">
+        <v>270</v>
+      </c>
       <c r="B271" s="0" t="s">
         <v>81</v>
       </c>
@@ -17486,13 +17495,13 @@
         <v>449</v>
       </c>
       <c r="S271" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T271" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="272">
+      <c r="A272" s="0">
+        <v>271</v>
+      </c>
       <c r="B272" s="0" t="s">
         <v>84</v>
       </c>
@@ -17506,7 +17515,7 @@
         <v>77</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G272" s="0">
         <v>10</v>
@@ -17545,13 +17554,13 @@
         <v>450</v>
       </c>
       <c r="S272" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T272" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="273">
+      <c r="A273" s="0">
+        <v>272</v>
+      </c>
       <c r="B273" s="0" t="s">
         <v>373</v>
       </c>
@@ -17604,13 +17613,13 @@
         <v>451</v>
       </c>
       <c r="S273" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T273" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="274">
+      <c r="A274" s="0">
+        <v>273</v>
+      </c>
       <c r="B274" s="0" t="s">
         <v>374</v>
       </c>
@@ -17624,7 +17633,7 @@
         <v>77</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G274" s="0">
         <v>10</v>
@@ -17663,13 +17672,13 @@
         <v>452</v>
       </c>
       <c r="S274" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T274" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="275">
+      <c r="A275" s="0">
+        <v>274</v>
+      </c>
       <c r="B275" s="0" t="s">
         <v>86</v>
       </c>
@@ -17722,13 +17731,13 @@
         <v>454</v>
       </c>
       <c r="S275" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T275" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="276">
+      <c r="A276" s="0">
+        <v>275</v>
+      </c>
       <c r="B276" s="0" t="s">
         <v>89</v>
       </c>
@@ -17742,7 +17751,7 @@
         <v>21</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G276" s="0">
         <v>70</v>
@@ -17781,13 +17790,13 @@
         <v>455</v>
       </c>
       <c r="S276" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T276" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="277">
+      <c r="A277" s="0">
+        <v>276</v>
+      </c>
       <c r="B277" s="0" t="s">
         <v>92</v>
       </c>
@@ -17840,13 +17849,13 @@
         <v>456</v>
       </c>
       <c r="S277" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T277" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="278">
+      <c r="A278" s="0">
+        <v>277</v>
+      </c>
       <c r="B278" s="0" t="s">
         <v>95</v>
       </c>
@@ -17899,13 +17908,13 @@
         <v>457</v>
       </c>
       <c r="S278" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T278" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="279">
+      <c r="A279" s="0">
+        <v>278</v>
+      </c>
       <c r="B279" s="0" t="s">
         <v>385</v>
       </c>
@@ -17919,7 +17928,7 @@
         <v>77</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G279" s="0">
         <v>10</v>
@@ -17958,13 +17967,13 @@
         <v>458</v>
       </c>
       <c r="S279" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T279" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="280">
+      <c r="A280" s="0">
+        <v>279</v>
+      </c>
       <c r="B280" s="0" t="s">
         <v>387</v>
       </c>
@@ -18017,13 +18026,13 @@
         <v>459</v>
       </c>
       <c r="S280" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T280" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="281">
+      <c r="A281" s="0">
+        <v>280</v>
+      </c>
       <c r="B281" s="0" t="s">
         <v>389</v>
       </c>
@@ -18076,13 +18085,13 @@
         <v>460</v>
       </c>
       <c r="S281" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T281" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="282">
+      <c r="A282" s="0">
+        <v>281</v>
+      </c>
       <c r="B282" s="0" t="s">
         <v>391</v>
       </c>
@@ -18135,13 +18144,13 @@
         <v>461</v>
       </c>
       <c r="S282" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T282" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="283">
+      <c r="A283" s="0">
+        <v>282</v>
+      </c>
       <c r="B283" s="0" t="s">
         <v>393</v>
       </c>
@@ -18194,13 +18203,13 @@
         <v>462</v>
       </c>
       <c r="S283" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T283" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="284">
+      <c r="A284" s="0">
+        <v>283</v>
+      </c>
       <c r="B284" s="0" t="s">
         <v>395</v>
       </c>
@@ -18214,7 +18223,7 @@
         <v>77</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G284" s="0">
         <v>40</v>
@@ -18253,13 +18262,13 @@
         <v>463</v>
       </c>
       <c r="S284" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T284" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="285">
+      <c r="A285" s="0">
+        <v>284</v>
+      </c>
       <c r="B285" s="0" t="s">
         <v>192</v>
       </c>
@@ -18312,13 +18321,13 @@
         <v>465</v>
       </c>
       <c r="S285" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T285" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="286">
+      <c r="A286" s="0">
+        <v>285</v>
+      </c>
       <c r="B286" s="0" t="s">
         <v>194</v>
       </c>
@@ -18332,7 +18341,7 @@
         <v>21</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G286" s="0">
         <v>60</v>
@@ -18371,13 +18380,13 @@
         <v>466</v>
       </c>
       <c r="S286" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T286" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="287">
+      <c r="A287" s="0">
+        <v>286</v>
+      </c>
       <c r="B287" s="0" t="s">
         <v>196</v>
       </c>
@@ -18430,13 +18439,13 @@
         <v>467</v>
       </c>
       <c r="S287" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T287" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="288">
+      <c r="A288" s="0">
+        <v>287</v>
+      </c>
       <c r="B288" s="0" t="s">
         <v>102</v>
       </c>
@@ -18489,13 +18498,13 @@
         <v>469</v>
       </c>
       <c r="S288" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T288" s="0">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289">
+      <c r="A289" s="0">
+        <v>288</v>
+      </c>
       <c r="B289" s="0" t="s">
         <v>105</v>
       </c>
@@ -18509,7 +18518,7 @@
         <v>77</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G289" s="0">
         <v>60</v>
@@ -18548,13 +18557,13 @@
         <v>470</v>
       </c>
       <c r="S289" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T289" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="290">
+      <c r="A290" s="0">
+        <v>289</v>
+      </c>
       <c r="B290" s="0" t="s">
         <v>107</v>
       </c>
@@ -18607,13 +18616,13 @@
         <v>471</v>
       </c>
       <c r="S290" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T290" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="291">
+      <c r="A291" s="0">
+        <v>290</v>
+      </c>
       <c r="B291" s="0" t="s">
         <v>109</v>
       </c>
@@ -18666,13 +18675,13 @@
         <v>472</v>
       </c>
       <c r="S291" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T291" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="292">
+      <c r="A292" s="0">
+        <v>291</v>
+      </c>
       <c r="B292" s="0" t="s">
         <v>112</v>
       </c>
@@ -18725,10 +18734,7 @@
         <v>473</v>
       </c>
       <c r="S292" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="T292" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
